--- a/backups/resumes.xlsx
+++ b/backups/resumes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -545,14 +545,68 @@
           <t>CEO (Google:OPP000001)</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>20LPA</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>RID02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Palak</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Naukri.com</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>PowerBI</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>No Resume Uploaded</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Merit</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Marketing (Facebook:OPP000002)</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>20LPA</t>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>44</t>
         </is>
       </c>
     </row>
